--- a/GameData/tables/07_Survivor.xlsx
+++ b/GameData/tables/07_Survivor.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="surv_wave" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'surv_param'!$A$1:$E$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'surv_param'!$A$1:$E$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'surv_combo'!$A$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'surv_set'!$A$1:$E$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'surv_wave'!$A$1:$K$11</definedName>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.2" customWidth="1" min="1" max="1"/>
@@ -2447,92 +2447,92 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>tornado</t>
+          <t>blender</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>combo</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>radiusMul</t>
+          <t>cd</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>흡입 소용돌이 반경 배율</t>
+          <t>칼날 회오리 간격(초)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>tornado</t>
+          <t>blender</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>combo</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>dpsMul</t>
+          <t>radius</t>
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>피해 배율</t>
+          <t>자기 주변 범위</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>tornado</t>
+          <t>blender</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>combo</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>dmg</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>0.4</v>
+        <v>16</v>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>안쪽 적 둔화</t>
+          <t>피해</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>blizzard</t>
+          <t>blender</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>combo</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>freeze</t>
+          <t>exec</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
@@ -2540,533 +2540,589 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>냉기 탄 명중 시 빙결(초)</t>
+          <t>체력 30% 이하 적 추가 피해</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>blizzard</t>
+          <t>blender</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>combo</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>pierce</t>
+          <t>perLv</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>관통 수</t>
+          <t>레벨당 강화</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>turbo</t>
+          <t>purifier</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>combo</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>countAdd</t>
+          <t>cd</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>브러시 추가 개수</t>
+          <t>정화 탄 간격(초)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>turbo</t>
+          <t>purifier</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>combo</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>spinMul</t>
+          <t>count</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>회전 속도 배율</t>
+          <t>한 번에 쏘는 수</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>turbo</t>
+          <t>purifier</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>combo</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>dmgMul</t>
+          <t>dmg</t>
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>1.5</v>
+        <v>20</v>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>피해 배율</t>
+          <t>피해(공중 2배)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>dust</t>
+          <t>purifier</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>contactDps</t>
+          <t>perLv</t>
         </is>
       </c>
       <c r="D85" s="6" t="n">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>닿아 있을 때 초당 내구도 피해</t>
+          <t>레벨당 강화</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>dust</t>
+          <t>router</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>xp</t>
+          <t>cd</t>
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>먼지 조각 경험치</t>
+          <t>연쇄 번개 간격(초)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>dust</t>
+          <t>router</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>speed</t>
+          <t>range</t>
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>이동 속도</t>
+          <t>사거리</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>fly</t>
+          <t>router</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>contactDps</t>
+          <t>chain</t>
         </is>
       </c>
       <c r="D88" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E88" s="5" t="inlineStr"/>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>튀는 수</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>fly</t>
+          <t>router</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>xp</t>
+          <t>dmg</t>
         </is>
       </c>
       <c r="D89" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="5" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>피해(튈 때마다 80%)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>fly</t>
+          <t>router</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>speed</t>
+          <t>perLv</t>
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E90" s="5" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>레벨당 강화</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>grease</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>contactDps</t>
+          <t>cd</t>
         </is>
       </c>
       <c r="D91" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E91" s="5" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>광고 시간 간격(초)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>grease</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>xp</t>
+          <t>radius</t>
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E92" s="5" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>반경(리더 중심)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>grease</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>speed</t>
+          <t>freeze</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E93" s="5" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>멈춤(초, 보스 1/3)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>mold</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>contactDps</t>
+          <t>dmg</t>
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="E94" s="5" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>피해</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>mold</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>comp</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>xp</t>
+          <t>perLv</t>
         </is>
       </c>
       <c r="D95" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E95" s="5" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>레벨당 강화</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>mold</t>
+          <t>tornado</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>combo</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>speed</t>
+          <t>radiusMul</t>
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E96" s="5" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>흡입 소용돌이 반경 배율</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>spore</t>
+          <t>tornado</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>combo</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>contactDps</t>
+          <t>dpsMul</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E97" s="5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>피해 배율</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>spore</t>
+          <t>tornado</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>combo</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>xp</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E98" s="5" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>안쪽 적 둔화</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>spore</t>
+          <t>blizzard</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>combo</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>speed</t>
+          <t>freeze</t>
         </is>
       </c>
       <c r="D99" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E99" s="5" t="inlineStr"/>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>냉기 탄 명중 시 빙결(초)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>mite</t>
+          <t>blizzard</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>combo</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>contactDps</t>
+          <t>pierce</t>
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>진드기: 약하지만 빠른 떼(10.16-f)</t>
+          <t>관통 수</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>mite</t>
+          <t>turbo</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>combo</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>xp</t>
+          <t>countAdd</t>
         </is>
       </c>
       <c r="D101" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>브러시 추가 개수</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>mite</t>
+          <t>turbo</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>combo</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>speed</t>
+          <t>spinMul</t>
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E102" s="5" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>회전 속도 배율</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>moth</t>
+          <t>turbo</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>enemy</t>
+          <t>combo</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>contactDps</t>
+          <t>dmgMul</t>
         </is>
       </c>
       <c r="D103" s="6" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>나방: 단단한 비행(10.16-f)</t>
+          <t>피해 배율</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>moth</t>
+          <t>dust</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -3076,18 +3132,22 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>xp</t>
+          <t>contactDps</t>
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E104" s="5" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>닿아 있을 때 초당 내구도 피해</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>moth</t>
+          <t>dust</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -3097,18 +3157,22 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>speed</t>
+          <t>xp</t>
         </is>
       </c>
       <c r="D105" s="6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E105" s="5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>먼지 조각 경험치</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>spore</t>
+          <t>dust</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -3118,22 +3182,22 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>range</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>원거리: 이 거리까지 다가와 멈추고 포자를 쏜다(칸)</t>
+          <t>이동 속도</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>spore</t>
+          <t>fly</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -3143,22 +3207,18 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>shotCd</t>
+          <t>contactDps</t>
         </is>
       </c>
       <c r="D107" s="6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>발사 간격(초)</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>spore</t>
+          <t>fly</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -3168,22 +3228,18 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>shotDmg</t>
+          <t>xp</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>포자 1발 피해(무한 강화의 피해 배율 적용)</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E108" s="5" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>spore</t>
+          <t>fly</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -3193,22 +3249,18 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>shotSpeed</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>포자 속도(칸/초). 리더(3칸/초)와 비슷해 옆으로 비켜서 피한다</t>
-        </is>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="E109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>boss_dust</t>
+          <t>grease</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -3222,14 +3274,14 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>boss_dust</t>
+          <t>grease</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -3243,14 +3295,14 @@
         </is>
       </c>
       <c r="D111" s="6" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>boss_dust</t>
+          <t>grease</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
@@ -3271,7 +3323,7 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>boss_grease</t>
+          <t>mold</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
@@ -3285,14 +3337,14 @@
         </is>
       </c>
       <c r="D113" s="6" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>boss_grease</t>
+          <t>mold</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
@@ -3306,14 +3358,14 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="E114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>boss_grease</t>
+          <t>mold</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -3327,14 +3379,14 @@
         </is>
       </c>
       <c r="D115" s="6" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="E115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>boss_mold</t>
+          <t>spore</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
@@ -3348,14 +3400,14 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>boss_mold</t>
+          <t>spore</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -3369,14 +3421,14 @@
         </is>
       </c>
       <c r="D117" s="6" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>boss_mold</t>
+          <t>spore</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
@@ -3390,137 +3442,560 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E118" s="5" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>move</t>
+          <t>mite</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>passive</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>contactDps</t>
         </is>
       </c>
       <c r="D119" s="6" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>이동 속도 증가(단계당)</t>
+          <t>진드기: 약하지만 빠른 떼(10.16-f)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>move</t>
+          <t>mite</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>passive</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>xp</t>
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>최대 단계</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>hp</t>
+          <t>mite</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>passive</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="D121" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>최대 내구도 증가(단계당, 증가분만큼 회복)</t>
-        </is>
-      </c>
+        <v>2.15</v>
+      </c>
+      <c r="E121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>hp</t>
+          <t>moth</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>passive</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>contactDps</t>
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>최대 단계</t>
+          <t>나방: 단단한 비행(10.16-f)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
+          <t>moth</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>moth</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>speed</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>spore</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>원거리: 이 거리까지 다가와 멈추고 포자를 쏜다(칸)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>spore</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>shotCd</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>발사 간격(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>spore</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>shotDmg</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>포자 1발 피해(무한 강화의 피해 배율 적용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>spore</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>shotSpeed</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>포자 속도(칸/초). 리더(3칸/초)와 비슷해 옆으로 비켜서 피한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>boss_dust</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>contactDps</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>boss_dust</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>boss_dust</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>speed</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>boss_grease</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>contactDps</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="E132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>boss_grease</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="E133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>boss_grease</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>speed</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>boss_mold</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>contactDps</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="E135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>boss_mold</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>boss_mold</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>speed</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E137" s="5" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>이동 속도 증가(단계당)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>최대 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>최대 내구도 증가(단계당, 증가분만큼 회복)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>최대 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
           <t>bonus</t>
         </is>
       </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="B142" s="5" t="inlineStr">
         <is>
           <t>passive</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C142" s="5" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="D123" s="6" t="n">
+      <c r="D142" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E123" s="5" t="inlineStr">
+      <c r="E142" s="5" t="inlineStr">
         <is>
           <t>뽑을 강화가 다 떨어진 뒤 레벨 업 보상: 코인(회복 없음. 무한 회복으로 영원히 버티는 걸 막는다)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E123"/>
+  <autoFilter ref="A1:E142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
